--- a/PUEYRREDON 1494/Diciembre/PUEYRREDON Diciembre.xlsx
+++ b/PUEYRREDON 1494/Diciembre/PUEYRREDON Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7045A808-10FA-4B14-BFAD-E3F10B2B487F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAF7197-6F60-4609-B3EA-4B281EAA8173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$108</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="163">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -63,15 +63,6 @@
     <t>HABERES ENCARGADOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Ayala Mirta Encargada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retenciones </t>
-  </si>
-  <si>
-    <t>Redondeo</t>
-  </si>
-  <si>
     <t>Neto</t>
   </si>
   <si>
@@ -471,42 +462,9 @@
     <t>PAULA</t>
   </si>
   <si>
-    <t>REVISAR QUE HUBO UN PROBLEMA CON EL 1B, EL MES PASADO LO HABIAMOS PUESTO CON UNA DEUDA ENORME CUANDO NO ERA CORRECTA</t>
-  </si>
-  <si>
-    <t>Matafuegos FIRE - Recarga de matafuegos</t>
-  </si>
-  <si>
-    <t>Transf 11/11</t>
-  </si>
-  <si>
-    <t>Debito 05/11</t>
-  </si>
-  <si>
-    <t>Debito 14/11</t>
-  </si>
-  <si>
-    <t>PMC 11/11</t>
-  </si>
-  <si>
-    <t>Debito 11/11</t>
-  </si>
-  <si>
-    <t>Debito 07/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve"> El dueño es sanabria - Gabriela San</t>
   </si>
   <si>
-    <t>HABIA PAGADO EL MES ANTERIOR $208.861,13</t>
-  </si>
-  <si>
     <t>Atriculos de limpieza</t>
   </si>
   <si>
@@ -535,6 +493,27 @@
   </si>
   <si>
     <t>Servisur - Instalacion de tortugas techo</t>
+  </si>
+  <si>
+    <t>PMC 05/12</t>
+  </si>
+  <si>
+    <t>Transf 04/12</t>
+  </si>
+  <si>
+    <t>Debito 12/12</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Debito 01/12</t>
+  </si>
+  <si>
+    <t>Se debe Diciembre</t>
+  </si>
+  <si>
+    <t>Ayala Mirta Encargada - La contadora no entrego la liquidacion de sueldo antes de irse de vacaciones por lo que se repite el monto salarial del mes anterior y en caso de existir diferencias reales, el mes siguiente se concilian las diferencias</t>
   </si>
 </sst>
 </file>
@@ -749,7 +728,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -816,6 +795,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1217,7 +1208,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1437,26 +1428,47 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="9" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="12" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="12" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="9" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="12" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="13" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="13" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="13" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1468,20 +1480,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1490,6 +1491,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1528,9 +1535,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1886,28 +1890,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M117"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="140"/>
       <c r="B1" s="141"/>
       <c r="C1" s="142"/>
       <c r="D1" s="142"/>
       <c r="E1" s="143"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="144"/>
       <c r="B2" s="136" t="s">
         <v>0</v>
@@ -1916,7 +1920,7 @@
       <c r="D2" s="136"/>
       <c r="E2" s="145"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="144"/>
       <c r="B3" s="136" t="s">
         <v>1</v>
@@ -1925,7 +1929,7 @@
       <c r="D3" s="136"/>
       <c r="E3" s="145"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="144"/>
       <c r="B4" s="137" t="s">
         <v>2</v>
@@ -1936,7 +1940,7 @@
       </c>
       <c r="E4" s="145"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="144" t="s">
         <v>4</v>
       </c>
@@ -1947,12 +1951,12 @@
       <c r="D5" s="135"/>
       <c r="E5" s="146"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="144" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="135" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C6" s="135"/>
       <c r="D6" s="136" t="s">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="E6" s="146"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="147" t="s">
         <v>8</v>
       </c>
@@ -1969,60 +1973,60 @@
       <c r="D7" s="148"/>
       <c r="E7" s="149"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="186" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="174"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="174"/>
-      <c r="C10" s="174"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="174"/>
-      <c r="C11" s="174"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="190" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="185"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="185"/>
+      <c r="C10" s="185"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="132"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="187" t="s">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="174"/>
-      <c r="B15" s="174"/>
-      <c r="C15" s="174"/>
-      <c r="D15" s="174"/>
-      <c r="E15" s="174"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="174"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="174"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
-      <c r="D17" s="174"/>
-      <c r="E17" s="174"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="185"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="185"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="185"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -2031,7 +2035,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
@@ -2040,877 +2044,814 @@
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="5"/>
+    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="194"/>
       <c r="C23" s="5"/>
       <c r="D23" s="120">
-        <v>898242.9</v>
+        <v>702876.00000000012</v>
       </c>
       <c r="E23" s="80"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="120">
-        <v>-195367.83</v>
+        <v>362730</v>
       </c>
       <c r="E24" s="80"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="120">
-        <v>0.93</v>
-      </c>
-      <c r="E25" s="80"/>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="121">
+        <f>SUM(D23:D24)</f>
+        <v>1065606</v>
+      </c>
+      <c r="E25" s="81"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="120"/>
       <c r="E26" s="80"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="57" t="s">
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="80"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="131">
+        <f>SUM(D26:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="81"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="82">
+        <f>D25+D28</f>
+        <v>1065606</v>
+      </c>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="83"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="121">
-        <f>SUM(D23:D26)</f>
-        <v>702876.00000000012</v>
-      </c>
-      <c r="E27" s="81"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="80"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="80"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="131">
-        <f>SUM(D28:D29)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="81"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="23" t="s">
+      <c r="B31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="120">
+        <v>39000</v>
+      </c>
+      <c r="E31" s="84"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="122"/>
-      <c r="E31" s="82">
-        <f>D27+D30</f>
-        <v>702876.00000000012</v>
-      </c>
-      <c r="F31" s="15"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="32" t="s">
+      <c r="B32" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="120">
+        <v>0</v>
+      </c>
+      <c r="E32" s="84"/>
+      <c r="H32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="123"/>
-      <c r="E32" s="83"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="64" t="s">
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="85">
+        <f>SUM(D31:D32)</f>
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="205">
-        <v>39000</v>
-      </c>
-      <c r="E33" s="84"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="66"/>
+    </row>
+    <row r="35" spans="1:7" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="192" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="120">
-        <v>143100</v>
-      </c>
-      <c r="E34" s="84"/>
-      <c r="H34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="23" t="s">
+      <c r="B35" s="188"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="153">
+        <v>87562.7</v>
+      </c>
+      <c r="E35" s="106" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="192" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="85">
-        <f>SUM(D33:D34)</f>
-        <v>182100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="B36" s="188"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="126">
+        <v>6646.91</v>
+      </c>
+      <c r="E36" s="106" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="66"/>
-    </row>
-    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="188" t="s">
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="86">
+        <f>SUM(D35:D36)</f>
+        <v>94209.61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="177"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="153">
-        <v>87562.7</v>
-      </c>
-      <c r="E37" s="106" t="s">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="87"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="126">
+        <v>431080.01</v>
+      </c>
+      <c r="E39" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" s="104"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="188" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" s="177"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="126">
-        <v>6646.91</v>
-      </c>
-      <c r="E38" s="106" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="23" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="86">
-        <f>SUM(D37:D38)</f>
-        <v>94209.61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="32" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="126">
+        <v>22456.07</v>
+      </c>
+      <c r="E40" s="108" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="str">
+        <f>A40</f>
+        <v>Sindicatos mes de DICIEMBRE</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="87"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="126">
+        <v>71517.789999999994</v>
+      </c>
+      <c r="E41" s="108" t="str">
+        <f>E40</f>
+        <v>Debito 12/12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="str">
+        <f>A41</f>
+        <v>Sindicatos mes de DICIEMBRE</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="204">
-        <v>431080.01</v>
-      </c>
-      <c r="E41" s="107" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="126">
+        <v>4491.21</v>
+      </c>
+      <c r="E42" s="109" t="str">
+        <f>E41</f>
+        <v>Debito 12/12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="86">
+        <f>SUM(D39:D42)</f>
+        <v>529545.07999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="127"/>
+      <c r="E44" s="87"/>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="126">
+        <v>51450</v>
+      </c>
+      <c r="E45" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="G41" s="104"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="204">
-        <v>22456.07</v>
-      </c>
-      <c r="E42" s="108" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="str">
-        <f>A42</f>
-        <v>Sindicatos mes de DICIEMBRE</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="126">
-        <v>70572.679999999993</v>
-      </c>
-      <c r="E43" s="108" t="str">
-        <f>E42</f>
-        <v>Debito 14/11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="str">
-        <f>A43</f>
-        <v>Sindicatos mes de DICIEMBRE</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="G45" s="112"/>
+    </row>
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="204">
-        <v>4491.21</v>
-      </c>
-      <c r="E44" s="109" t="str">
-        <f>E43</f>
-        <v>Debito 14/11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="23" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="126">
+        <v>167323.94</v>
+      </c>
+      <c r="E46" s="90" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="128"/>
-      <c r="E45" s="86">
-        <f>SUM(D41:D44)</f>
-        <v>528599.97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="127"/>
-      <c r="E46" s="87"/>
-    </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="53" t="s">
-        <v>166</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="204">
-        <v>51450</v>
-      </c>
-      <c r="E47" s="90" t="s">
-        <v>167</v>
-      </c>
-      <c r="G47" s="112"/>
-    </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D47" s="126"/>
+      <c r="E47" s="90"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="204">
-        <v>167323.94</v>
+      <c r="D48" s="126">
+        <v>46950</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="126">
-        <v>786.13</v>
+        <v>40000</v>
       </c>
       <c r="E49" s="90" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="160"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="159">
+        <v>20000</v>
+      </c>
+      <c r="E50" s="90" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="187"/>
+      <c r="B51" s="188"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="159"/>
+      <c r="E51" s="90"/>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="86">
+        <f>SUM(D45:D51)</f>
+        <v>325723.94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="89"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="53"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="88"/>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="126">
-        <v>786.13</v>
-      </c>
-      <c r="E50" s="90" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="204">
-        <v>46950</v>
-      </c>
-      <c r="E51" s="90" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="204">
-        <v>40000</v>
-      </c>
-      <c r="E52" s="90" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B53" s="160"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="206">
-        <v>20000</v>
-      </c>
-      <c r="E53" s="90" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="176" t="s">
-        <v>149</v>
-      </c>
-      <c r="B54" s="177"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="159">
-        <v>109699.95</v>
-      </c>
-      <c r="E54" s="90" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="23" t="s">
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="92">
+        <f>SUM(D54:D54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="86">
-        <f>SUM(D47:D54)</f>
-        <v>436996.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B56" s="23"/>
+      <c r="B56" s="65"/>
       <c r="C56" s="23"/>
-      <c r="D56" s="124"/>
+      <c r="D56" s="122"/>
       <c r="E56" s="89"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="53"/>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="88"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="92">
-        <f>SUM(D57:D57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="65"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="122"/>
-      <c r="E59" s="89"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="D57" s="126">
+        <v>69623.27</v>
+      </c>
+      <c r="E57" s="93"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="126">
+        <v>61600</v>
+      </c>
+      <c r="E58" s="91"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="94"/>
+      <c r="E59" s="86">
+        <f>SUM(D57:D58)</f>
+        <v>131223.27000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="126">
-        <v>59371.85</v>
-      </c>
-      <c r="E60" s="93"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
+      <c r="D60" s="80"/>
+      <c r="E60" s="95"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="97"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="D62" s="98"/>
+      <c r="E62" s="99"/>
+      <c r="F62" s="43"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="10"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="100"/>
+      <c r="E63" s="101">
+        <f>(SUM(E29:E61))</f>
+        <v>2185307.9</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="112"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D64" s="98"/>
+      <c r="E64" s="98"/>
+      <c r="G64" s="112"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="98"/>
+      <c r="E65" s="98"/>
+    </row>
+    <row r="66" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="126">
-        <v>56000</v>
-      </c>
-      <c r="E61" s="91"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
-      <c r="D62" s="94"/>
-      <c r="E62" s="86">
-        <f>SUM(D60:D61)</f>
-        <v>115371.85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="80"/>
-      <c r="E63" s="95"/>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="25" t="s">
+      <c r="B66" s="12"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="102"/>
+      <c r="E66" s="103"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="187"/>
+      <c r="B67" s="188"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="130"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="50"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="152">
+        <f>SUM(D67:D67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="96"/>
-      <c r="E64" s="97">
-        <f>4000000-1814491.63</f>
-        <v>2185508.37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1"/>
-      <c r="D65" s="98"/>
-      <c r="E65" s="99"/>
-      <c r="F65" s="43"/>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="113"/>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="100"/>
-      <c r="E66" s="101">
-        <f>(SUM(E31:E64))</f>
-        <v>4245661.95</v>
-      </c>
-      <c r="F66" s="43"/>
-      <c r="G66" s="112"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D67" s="98"/>
-      <c r="E67" s="98"/>
-      <c r="G67" s="112"/>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D68" s="98"/>
-      <c r="E68" s="98"/>
-    </row>
-    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="B72" s="10"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="67">
+        <f>E68+E70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="102"/>
-      <c r="E69" s="103"/>
-    </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="176" t="s">
-        <v>156</v>
-      </c>
-      <c r="B70" s="178"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="182">
-        <v>181000</v>
-      </c>
-      <c r="E70" s="184"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="179"/>
-      <c r="B71" s="180"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="183"/>
-      <c r="E71" s="185"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="176"/>
-      <c r="B72" s="177"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="130"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="50"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="152">
-        <f>SUM(D70:D72)</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="25" t="s">
+      <c r="B74" s="79">
+        <f>E63</f>
+        <v>2185307.9</v>
+      </c>
+      <c r="D74" s="43"/>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="113"/>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
+      <c r="B75" s="79">
+        <f>E63-E61</f>
+        <v>2185307.9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="67">
-        <f>E73+E75</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="78" t="s">
+      <c r="B76" s="79">
+        <f>E72-E70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B79" s="79">
-        <f>E66</f>
-        <v>4245661.95</v>
-      </c>
-      <c r="D79" s="43"/>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="78" t="s">
+      <c r="B77" s="79">
+        <f>E72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="184"/>
+      <c r="B80" s="185"/>
+      <c r="C80" s="185"/>
+      <c r="D80" s="185"/>
+      <c r="E80" s="185"/>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="185"/>
+      <c r="B81" s="185"/>
+      <c r="C81" s="185"/>
+      <c r="D81" s="185"/>
+      <c r="E81" s="185"/>
+    </row>
+    <row r="82" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="185"/>
+      <c r="B82" s="185"/>
+      <c r="C82" s="185"/>
+      <c r="D82" s="185"/>
+      <c r="E82" s="185"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B80" s="79">
-        <f>E66-E64</f>
-        <v>2060153.58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="78" t="s">
+      <c r="B84" s="38"/>
+      <c r="C84" s="17"/>
+    </row>
+    <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B81" s="79">
-        <f>E77-E75</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="78" t="s">
+      <c r="B85" s="111">
+        <v>4328491.5724999998</v>
+      </c>
+      <c r="C85" s="19"/>
+    </row>
+    <row r="86" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B82" s="79">
-        <f>E77</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="173"/>
-      <c r="B85" s="174"/>
-      <c r="C85" s="174"/>
-      <c r="D85" s="174"/>
-      <c r="E85" s="174"/>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="174"/>
-      <c r="B86" s="174"/>
-      <c r="C86" s="174"/>
-      <c r="D86" s="174"/>
-      <c r="E86" s="174"/>
-    </row>
-    <row r="87" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="174"/>
-      <c r="B87" s="174"/>
-      <c r="C87" s="174"/>
-      <c r="D87" s="174"/>
-      <c r="E87" s="174"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="16" t="s">
+      <c r="B86" s="39">
+        <f>PRORRATEO!H25</f>
+        <v>5379748.5700000003</v>
+      </c>
+      <c r="C86" s="17"/>
+    </row>
+    <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="150" t="s">
+        <v>139</v>
+      </c>
+      <c r="B87" s="47"/>
+      <c r="C87" s="17"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="181" t="s">
         <v>48</v>
       </c>
-      <c r="B89" s="38"/>
+      <c r="B88" s="91">
+        <f>B107</f>
+        <v>0</v>
+      </c>
+      <c r="C88" s="17"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" s="47">
+        <f>-B75</f>
+        <v>-2185307.9</v>
+      </c>
       <c r="C89" s="17"/>
-    </row>
-    <row r="90" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B90" s="111">
-        <v>1665135.9325000001</v>
-      </c>
-      <c r="C90" s="19"/>
-    </row>
-    <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="18" t="s">
+      <c r="E89" s="43"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B91" s="39">
-        <f>PRORRATEO!H25</f>
-        <v>4658847.2699999996</v>
-      </c>
-      <c r="C91" s="17"/>
-    </row>
-    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="150" t="s">
-        <v>142</v>
-      </c>
-      <c r="B92" s="47"/>
-      <c r="C92" s="17"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="18" t="s">
+      <c r="B90" s="47">
+        <f>-(B76)</f>
+        <v>0</v>
+      </c>
+      <c r="C90" s="17"/>
+      <c r="E90" s="19"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="110">
+        <f>SUM(B85:B90)</f>
+        <v>7522932.2424999997</v>
+      </c>
+      <c r="C91" s="20"/>
+    </row>
+    <row r="92" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="40"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="43"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="41"/>
+      <c r="C93" s="20"/>
+    </row>
+    <row r="94" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="40"/>
+      <c r="C94" s="35"/>
+    </row>
+    <row r="95" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B93" s="91">
-        <f>B112</f>
-        <v>0</v>
-      </c>
-      <c r="C93" s="17"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="37" t="s">
+      <c r="B95" s="33"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="46"/>
+    </row>
+    <row r="96" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B96" s="34">
+        <v>0</v>
+      </c>
+      <c r="C96" s="35"/>
+    </row>
+    <row r="97" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B94" s="47">
-        <f>-B80</f>
-        <v>-2060153.58</v>
-      </c>
-      <c r="C94" s="17"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B95" s="47">
-        <f>-(B81)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C95" s="17"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B96" s="110">
-        <f>SUM(B90:B95)</f>
-        <v>4082829.6224999996</v>
-      </c>
-      <c r="C96" s="20"/>
-    </row>
-    <row r="97" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="40"/>
+      <c r="B97" s="33">
+        <v>0</v>
+      </c>
       <c r="C97" s="20"/>
       <c r="D97" s="43"/>
     </row>
-    <row r="98" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="41"/>
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" s="33">
+        <v>0</v>
+      </c>
       <c r="C98" s="20"/>
     </row>
-    <row r="99" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="40"/>
-      <c r="C99" s="35"/>
-    </row>
-    <row r="100" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B99" s="33">
+        <v>0</v>
+      </c>
+      <c r="C99" s="22"/>
+    </row>
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B100" s="48">
+        <f>SUM(B96:B99)</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="17"/>
+    </row>
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="B100" s="33"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="46"/>
-    </row>
-    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B101" s="34">
-        <v>0</v>
-      </c>
-      <c r="C101" s="35"/>
-    </row>
-    <row r="102" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B102" s="33">
-        <v>0</v>
-      </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="43"/>
-    </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B103" s="33">
-        <v>0</v>
-      </c>
-      <c r="C103" s="20"/>
-    </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B104" s="33">
-        <v>0</v>
-      </c>
-      <c r="C104" s="22"/>
-    </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B105" s="48">
-        <f>SUM(B101:B104)</f>
-        <v>0</v>
-      </c>
-      <c r="C105" s="17"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="175" t="s">
-        <v>57</v>
-      </c>
-      <c r="B108" s="174"/>
-      <c r="C108" s="174"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="174"/>
-      <c r="B109" s="174"/>
-      <c r="C109" s="174"/>
-    </row>
-    <row r="110" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="55"/>
-      <c r="B110" s="33"/>
-      <c r="C110" s="33">
+      <c r="B103" s="185"/>
+      <c r="C103" s="185"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="185"/>
+      <c r="B104" s="185"/>
+      <c r="C104" s="185"/>
+    </row>
+    <row r="105" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="55"/>
+      <c r="B105" s="33"/>
+      <c r="C105" s="33">
         <v>40000</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="55"/>
-      <c r="B111" s="33"/>
-      <c r="C111" s="40"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B112" s="105">
-        <f>SUM(B110:B111)</f>
-        <v>0</v>
-      </c>
-      <c r="C112" s="45"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M113" s="8"/>
-    </row>
-    <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="181"/>
-      <c r="B114" s="174"/>
-      <c r="C114" s="174"/>
-      <c r="D114" s="174"/>
-      <c r="E114" s="174"/>
-    </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="174"/>
-      <c r="B115" s="174"/>
-      <c r="C115" s="174"/>
-      <c r="D115" s="174"/>
-      <c r="E115" s="174"/>
-    </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="174"/>
-      <c r="B116" s="174"/>
-      <c r="C116" s="174"/>
-      <c r="D116" s="174"/>
-      <c r="E116" s="174"/>
-    </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="174"/>
-      <c r="B117" s="174"/>
-      <c r="C117" s="174"/>
-      <c r="D117" s="174"/>
-      <c r="E117" s="174"/>
+    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="55"/>
+      <c r="B106" s="33"/>
+      <c r="C106" s="40"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B107" s="105">
+        <f>SUM(B105:B106)</f>
+        <v>0</v>
+      </c>
+      <c r="C107" s="45"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M108" s="8"/>
+    </row>
+    <row r="109" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="189"/>
+      <c r="B109" s="185"/>
+      <c r="C109" s="185"/>
+      <c r="D109" s="185"/>
+      <c r="E109" s="185"/>
+    </row>
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="185"/>
+      <c r="B110" s="185"/>
+      <c r="C110" s="185"/>
+      <c r="D110" s="185"/>
+      <c r="E110" s="185"/>
+    </row>
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="185"/>
+      <c r="B111" s="185"/>
+      <c r="C111" s="185"/>
+      <c r="D111" s="185"/>
+      <c r="E111" s="185"/>
+    </row>
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="185"/>
+      <c r="B112" s="185"/>
+      <c r="C112" s="185"/>
+      <c r="D112" s="185"/>
+      <c r="E112" s="185"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="10">
+    <mergeCell ref="A80:E82"/>
+    <mergeCell ref="A103:C104"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A109:E112"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A85:E87"/>
-    <mergeCell ref="A108:C109"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A70:B71"/>
-    <mergeCell ref="A114:E117"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2921,52 +2862,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="201" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="174"/>
-      <c r="O1" s="174"/>
+      <c r="F1" s="207" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="185"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2982,23 +2923,23 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="195">
+      <c r="O2" s="201">
         <f>T4</f>
-        <v>4000000</v>
-      </c>
-      <c r="P2" s="174"/>
+        <v>2185307.9</v>
+      </c>
+      <c r="P2" s="185"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -3008,109 +2949,109 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="199">
+      <c r="O3" s="205">
         <f>S6</f>
-        <v>181000</v>
-      </c>
-      <c r="P3" s="200"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="189" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="206"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="195" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="202" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="197" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="197" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="196" t="s">
+      <c r="E4" s="198" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="191" t="s">
+      <c r="F4" s="197" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="191" t="s">
+      <c r="G4" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="192" t="s">
+      <c r="H4" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="191" t="s">
+      <c r="I4" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="191" t="s">
+      <c r="J4" s="208" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="191" t="s">
+      <c r="K4" s="200" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="192" t="s">
+      <c r="L4" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="202" t="s">
+      <c r="M4" s="200" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="194" t="s">
+      <c r="N4" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="O4" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="194" t="s">
+      <c r="P4" s="204" t="s">
         <v>75</v>
-      </c>
-      <c r="N4" s="194" t="s">
-        <v>76</v>
-      </c>
-      <c r="O4" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" s="198" t="s">
-        <v>78</v>
       </c>
       <c r="S4" s="43"/>
       <c r="T4">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="190"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="193"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="190"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
-      <c r="K5" s="193"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="193"/>
-      <c r="N5" s="193"/>
+        <v>2185307.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="196"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="199"/>
+      <c r="N5" s="199"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="P5" s="190"/>
+      <c r="P5" s="196"/>
       <c r="T5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B6" s="62">
         <v>1</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F6" s="68">
         <v>3</v>
@@ -3133,62 +3074,58 @@
       </c>
       <c r="L6" s="72">
         <f t="shared" ref="L6:L24" si="2">O$3*F6%</f>
-        <v>5430</v>
+        <v>0</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6:M24" si="3">O$2*F6%</f>
-        <v>120000</v>
+        <v>65559.236999999994</v>
       </c>
       <c r="N6" s="114">
         <f t="shared" ref="N6:N24" si="4">SUM(J6:M6)</f>
-        <v>125430</v>
+        <v>65559.236999999994</v>
       </c>
       <c r="O6" s="118" t="str">
         <f t="shared" ref="O6:O24" si="5">CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
-        <v>$125430,1</v>
+        <v>$65559,1</v>
       </c>
       <c r="P6" s="119" t="str">
         <f t="shared" ref="P6:P24" si="6">CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
-        <v>$129193,1</v>
+        <v>$67526,1</v>
       </c>
       <c r="Q6" s="43" t="str">
         <f t="shared" ref="Q6:Q24" si="7">CONCATENATE(B6)</f>
         <v>1</v>
       </c>
-      <c r="S6">
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B7" s="62">
         <v>2</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F7" s="68">
         <v>3.8</v>
       </c>
       <c r="G7" s="133">
-        <v>325700.2</v>
+        <v>153580.20000000001</v>
       </c>
       <c r="H7" s="129">
-        <f>335471.02</f>
-        <v>335471.02</v>
+        <v>154000</v>
       </c>
       <c r="I7" s="70"/>
       <c r="J7" s="117">
         <f t="shared" si="0"/>
-        <v>-9770.820000000007</v>
+        <v>-419.79999999998836</v>
       </c>
       <c r="K7" s="71">
         <f t="shared" si="1"/>
@@ -3196,23 +3133,23 @@
       </c>
       <c r="L7" s="72">
         <f t="shared" si="2"/>
-        <v>6878</v>
+        <v>0</v>
       </c>
       <c r="M7" s="72">
         <f t="shared" si="3"/>
-        <v>152000</v>
+        <v>83041.700199999992</v>
       </c>
       <c r="N7" s="114">
         <f t="shared" si="4"/>
-        <v>149107.18</v>
+        <v>82621.900200000004</v>
       </c>
       <c r="O7" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$149107,2</v>
+        <v>$82622,2</v>
       </c>
       <c r="P7" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$153580,2</v>
+        <v>$85101,2</v>
       </c>
       <c r="Q7" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3220,120 +3157,116 @@
       </c>
       <c r="R7" s="43"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" s="62">
         <v>3</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F8" s="68">
         <v>3</v>
       </c>
       <c r="G8" s="133">
-        <v>240863.3</v>
-      </c>
-      <c r="H8" s="129">
-        <f>100000+48089.3</f>
-        <v>148089.29999999999</v>
-      </c>
+        <v>222843.3</v>
+      </c>
+      <c r="H8" s="129"/>
       <c r="I8" s="70"/>
       <c r="J8" s="117">
         <f t="shared" si="0"/>
-        <v>92774</v>
+        <v>222843.3</v>
       </c>
       <c r="K8" s="71">
         <f t="shared" si="1"/>
-        <v>4638.7</v>
+        <v>11142.165000000001</v>
       </c>
       <c r="L8" s="72">
         <f t="shared" si="2"/>
-        <v>5430</v>
+        <v>0</v>
       </c>
       <c r="M8" s="72">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>65559.236999999994</v>
       </c>
       <c r="N8" s="114">
         <f t="shared" si="4"/>
-        <v>222842.7</v>
+        <v>299544.70199999999</v>
       </c>
       <c r="O8" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$222843,3</v>
+        <v>$299545,3</v>
       </c>
       <c r="P8" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$229528,3</v>
+        <v>$308531,3</v>
       </c>
       <c r="Q8" s="43" t="str">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B9" s="62">
         <v>4</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E9" s="62" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F9" s="68">
         <v>3.1</v>
       </c>
       <c r="G9" s="133">
-        <v>133500.4</v>
+        <v>133499.4</v>
       </c>
       <c r="H9" s="129">
-        <f t="shared" ref="H9:H14" si="8">G9</f>
-        <v>133500.4</v>
+        <v>130000</v>
       </c>
       <c r="I9" s="70"/>
       <c r="J9" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3499.3999999999942</v>
       </c>
       <c r="K9" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>174.96999999999971</v>
       </c>
       <c r="L9" s="72">
         <f t="shared" si="2"/>
-        <v>5611</v>
+        <v>0</v>
       </c>
       <c r="M9" s="72">
         <f t="shared" si="3"/>
-        <v>124000</v>
+        <v>67744.544899999994</v>
       </c>
       <c r="N9" s="114">
         <f t="shared" si="4"/>
-        <v>129611</v>
+        <v>71418.914899999989</v>
       </c>
       <c r="O9" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$129611,4</v>
+        <v>$71419,4</v>
       </c>
       <c r="P9" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$133499,4</v>
+        <v>$73561,4</v>
       </c>
       <c r="Q9" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3341,34 +3274,34 @@
       </c>
       <c r="S9" s="43"/>
       <c r="T9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B10" s="62">
         <v>5</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F10" s="68">
         <v>3.1</v>
       </c>
       <c r="G10" s="129">
-        <v>633734.5</v>
+        <v>133499.5</v>
       </c>
       <c r="H10" s="129">
-        <f t="shared" si="8"/>
-        <v>633734.5</v>
+        <f t="shared" ref="H10:H14" si="8">G10</f>
+        <v>133499.5</v>
       </c>
       <c r="I10" s="70"/>
       <c r="J10" s="117">
@@ -3381,23 +3314,23 @@
       </c>
       <c r="L10" s="72">
         <f t="shared" si="2"/>
-        <v>5611</v>
+        <v>0</v>
       </c>
       <c r="M10" s="72">
         <f t="shared" si="3"/>
-        <v>124000</v>
+        <v>67744.544899999994</v>
       </c>
       <c r="N10" s="114">
         <f t="shared" si="4"/>
-        <v>129611</v>
+        <v>67744.544899999994</v>
       </c>
       <c r="O10" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$129611,5</v>
+        <v>$67745,5</v>
       </c>
       <c r="P10" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$133499,5</v>
+        <v>$69777,5</v>
       </c>
       <c r="Q10" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3405,18 +3338,18 @@
       </c>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B11" s="62">
         <v>6</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E11" s="62"/>
       <c r="F11" s="68">
@@ -3440,44 +3373,44 @@
       </c>
       <c r="L11" s="72">
         <f t="shared" si="2"/>
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="M11" s="72">
         <f t="shared" si="3"/>
-        <v>128000</v>
+        <v>69929.852799999993</v>
       </c>
       <c r="N11" s="114">
         <f t="shared" si="4"/>
-        <v>133792</v>
+        <v>69929.852799999993</v>
       </c>
       <c r="O11" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$133792,6</v>
+        <v>$69930,6</v>
       </c>
       <c r="P11" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$137806,6</v>
+        <v>$72028,6</v>
       </c>
       <c r="Q11" s="43" t="str">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B12" s="62">
         <v>7</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E12" s="62" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F12" s="68">
         <v>3.3</v>
@@ -3500,117 +3433,116 @@
       </c>
       <c r="L12" s="72">
         <f t="shared" si="2"/>
-        <v>5973</v>
+        <v>0</v>
       </c>
       <c r="M12" s="72">
         <f t="shared" si="3"/>
-        <v>132000</v>
+        <v>72115.160699999993</v>
       </c>
       <c r="N12" s="114">
         <f t="shared" si="4"/>
-        <v>137973</v>
+        <v>72115.160699999993</v>
       </c>
       <c r="O12" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$137973,7</v>
+        <v>$72115,7</v>
       </c>
       <c r="P12" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$142112,7</v>
+        <v>$74279,7</v>
       </c>
       <c r="Q12" s="43" t="str">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B13" s="62">
         <v>23</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F13" s="68">
         <v>6.3</v>
       </c>
       <c r="G13" s="133">
-        <v>274746.23</v>
+        <v>271305.23</v>
       </c>
       <c r="H13" s="69">
-        <f t="shared" si="8"/>
-        <v>274746.23</v>
+        <v>252000</v>
       </c>
       <c r="I13" s="70"/>
       <c r="J13" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19305.229999999981</v>
       </c>
       <c r="K13" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>965.26149999999916</v>
       </c>
       <c r="L13" s="72">
         <f t="shared" si="2"/>
-        <v>11403</v>
+        <v>0</v>
       </c>
       <c r="M13" s="72">
         <f t="shared" si="3"/>
-        <v>252000</v>
+        <v>137674.3977</v>
       </c>
       <c r="N13" s="114">
         <f t="shared" si="4"/>
-        <v>263403</v>
+        <v>157944.88919999998</v>
       </c>
       <c r="O13" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$263403,23</v>
+        <v>$157945,23</v>
       </c>
       <c r="P13" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$271305,23</v>
+        <v>$162683,23</v>
       </c>
       <c r="Q13" s="43" t="str">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="151">
         <v>22</v>
       </c>
       <c r="C14" s="151" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D14" s="151" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E14" s="151" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F14" s="154">
         <v>5.0999999999999996</v>
       </c>
       <c r="G14" s="134">
-        <v>211462.22</v>
+        <v>213231.22</v>
       </c>
       <c r="H14" s="69">
         <f t="shared" si="8"/>
-        <v>211462.22</v>
+        <v>213231.22</v>
       </c>
       <c r="I14" s="70"/>
       <c r="J14" s="117">
@@ -3623,104 +3555,99 @@
       </c>
       <c r="L14" s="155">
         <f t="shared" si="2"/>
-        <v>9231</v>
+        <v>0</v>
       </c>
       <c r="M14" s="155">
         <f t="shared" si="3"/>
-        <v>204000</v>
+        <v>111450.70289999999</v>
       </c>
       <c r="N14" s="156">
         <f t="shared" si="4"/>
-        <v>213231</v>
+        <v>111450.70289999999</v>
       </c>
       <c r="O14" s="157" t="str">
         <f t="shared" si="5"/>
-        <v>$213231,22</v>
+        <v>$111451,22</v>
       </c>
       <c r="P14" s="158" t="str">
         <f t="shared" si="6"/>
-        <v>$219628,22</v>
+        <v>$114794,22</v>
       </c>
       <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="R14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B15" s="62">
         <v>21</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D15" s="62" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E15" s="63"/>
       <c r="F15" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G15" s="133">
-        <v>353127.21</v>
-      </c>
-      <c r="H15" s="69">
-        <v>353127.21</v>
-      </c>
+        <v>342842.21</v>
+      </c>
+      <c r="H15" s="69"/>
       <c r="I15" s="70"/>
       <c r="J15" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>342842.21</v>
       </c>
       <c r="K15" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17142.110500000003</v>
       </c>
       <c r="L15" s="72">
         <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
+        <v>0</v>
       </c>
       <c r="M15" s="72">
         <f t="shared" si="3"/>
-        <v>327999.99999999994</v>
+        <v>179195.24779999998</v>
       </c>
       <c r="N15" s="114">
         <f t="shared" si="4"/>
-        <v>342841.99999999994</v>
+        <v>539179.56830000004</v>
       </c>
       <c r="O15" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$342842,21</v>
+        <v>$539180,21</v>
       </c>
       <c r="P15" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$353127,21</v>
+        <v>$555355,21</v>
       </c>
       <c r="Q15" s="43" t="str">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B16" s="62">
         <v>14</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F16" s="68">
         <v>6.1</v>
@@ -3729,13 +3656,12 @@
         <v>255041.14</v>
       </c>
       <c r="H16" s="69">
-        <f>G16</f>
-        <v>255041.14</v>
+        <v>262692.14</v>
       </c>
       <c r="I16" s="70"/>
       <c r="J16" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7651</v>
       </c>
       <c r="K16" s="71">
         <f t="shared" si="1"/>
@@ -3743,234 +3669,234 @@
       </c>
       <c r="L16" s="72">
         <f t="shared" si="2"/>
-        <v>11041</v>
+        <v>0</v>
       </c>
       <c r="M16" s="72">
         <f t="shared" si="3"/>
-        <v>244000</v>
+        <v>133303.7819</v>
       </c>
       <c r="N16" s="114">
         <f t="shared" si="4"/>
-        <v>255041</v>
+        <v>125652.7819</v>
       </c>
       <c r="O16" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$255041,14</v>
+        <v>$125653,14</v>
       </c>
       <c r="P16" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$262692,14</v>
+        <v>$129422,14</v>
       </c>
       <c r="Q16" s="43" t="str">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="161">
+        <v>113</v>
+      </c>
+      <c r="B17" s="151">
         <v>13</v>
       </c>
-      <c r="C17" s="161" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="161" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="162"/>
-      <c r="F17" s="163">
+      <c r="C17" s="151" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="151" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="161"/>
+      <c r="F17" s="154">
         <v>5</v>
       </c>
-      <c r="G17" s="164">
-        <v>208861.13</v>
-      </c>
-      <c r="H17" s="165">
+      <c r="G17" s="134">
+        <v>209050.13</v>
+      </c>
+      <c r="H17" s="69">
         <f>G17</f>
-        <v>208861.13</v>
-      </c>
-      <c r="I17" s="166"/>
-      <c r="J17" s="167">
+        <v>209050.13</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="167">
+      <c r="K17" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="168">
+      <c r="L17" s="155">
         <f t="shared" si="2"/>
-        <v>9050</v>
-      </c>
-      <c r="M17" s="168">
+        <v>0</v>
+      </c>
+      <c r="M17" s="155">
         <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-      <c r="N17" s="169">
+        <v>109265.395</v>
+      </c>
+      <c r="N17" s="156">
         <f t="shared" si="4"/>
-        <v>209050</v>
-      </c>
-      <c r="O17" s="170" t="str">
+        <v>109265.395</v>
+      </c>
+      <c r="O17" s="157" t="str">
         <f t="shared" si="5"/>
-        <v>$209050,13</v>
-      </c>
-      <c r="P17" s="171" t="str">
+        <v>$109265,13</v>
+      </c>
+      <c r="P17" s="158" t="str">
         <f t="shared" si="6"/>
-        <v>$215322,13</v>
+        <v>$112543,13</v>
       </c>
       <c r="Q17" s="43" t="str">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="S17" s="172" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S17" s="104"/>
+    </row>
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="162">
+        <v>12</v>
+      </c>
+      <c r="C18" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="62">
-        <v>12</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="62" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="68">
+      <c r="D18" s="162" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="162" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="163">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G18" s="133">
-        <v>17481584.120000001</v>
-      </c>
-      <c r="H18" s="69">
+      <c r="G18" s="164">
         <v>342842</v>
       </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="117">
+      <c r="H18" s="182">
+        <v>342842</v>
+      </c>
+      <c r="I18" s="165"/>
+      <c r="J18" s="166">
         <f t="shared" si="0"/>
-        <v>17138742.120000001</v>
-      </c>
-      <c r="K18" s="71">
+        <v>0</v>
+      </c>
+      <c r="K18" s="166">
         <f t="shared" si="1"/>
-        <v>856937.10600000015</v>
-      </c>
-      <c r="L18" s="72">
+        <v>0</v>
+      </c>
+      <c r="L18" s="167">
         <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
-      </c>
-      <c r="M18" s="72">
+        <v>0</v>
+      </c>
+      <c r="M18" s="167">
         <f t="shared" si="3"/>
-        <v>327999.99999999994</v>
-      </c>
-      <c r="N18" s="114">
+        <v>179195.24779999998</v>
+      </c>
+      <c r="N18" s="168">
         <f t="shared" si="4"/>
-        <v>18338521.226</v>
-      </c>
-      <c r="O18" s="116" t="str">
+        <v>179195.24779999998</v>
+      </c>
+      <c r="O18" s="169" t="str">
         <f t="shared" si="5"/>
-        <v>$18338521,12</v>
-      </c>
-      <c r="P18" s="119" t="str">
+        <v>$179195,12</v>
+      </c>
+      <c r="P18" s="170" t="str">
         <f t="shared" si="6"/>
-        <v>$18888677,12</v>
+        <v>$184571,12</v>
       </c>
       <c r="Q18" s="43" t="str">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="62">
+        <v>119</v>
+      </c>
+      <c r="B19" s="171">
         <v>17</v>
       </c>
-      <c r="C19" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="62" t="s">
+      <c r="C19" s="171" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="63"/>
-      <c r="F19" s="68">
+      <c r="D19" s="171" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="172"/>
+      <c r="F19" s="173">
         <v>6.1</v>
       </c>
-      <c r="G19" s="133">
-        <v>13365763.17</v>
-      </c>
-      <c r="H19" s="69"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="117">
+      <c r="G19" s="174">
+        <v>2180502.66</v>
+      </c>
+      <c r="H19" s="183">
+        <f>G19</f>
+        <v>2180502.66</v>
+      </c>
+      <c r="I19" s="175"/>
+      <c r="J19" s="176">
         <f t="shared" si="0"/>
-        <v>13365763.17</v>
-      </c>
-      <c r="K19" s="71">
+        <v>0</v>
+      </c>
+      <c r="K19" s="176">
         <f t="shared" si="1"/>
-        <v>668288.15850000002</v>
-      </c>
-      <c r="L19" s="72">
+        <v>0</v>
+      </c>
+      <c r="L19" s="177">
         <f t="shared" si="2"/>
-        <v>11041</v>
-      </c>
-      <c r="M19" s="72">
+        <v>0</v>
+      </c>
+      <c r="M19" s="177">
         <f t="shared" si="3"/>
-        <v>244000</v>
-      </c>
-      <c r="N19" s="114">
+        <v>133303.7819</v>
+      </c>
+      <c r="N19" s="178">
         <f t="shared" si="4"/>
-        <v>14289092.328500001</v>
-      </c>
-      <c r="O19" s="116" t="str">
+        <v>133303.7819</v>
+      </c>
+      <c r="O19" s="179" t="str">
         <f t="shared" si="5"/>
-        <v>$14289092,17</v>
-      </c>
-      <c r="P19" s="119" t="str">
+        <v>$133304,17</v>
+      </c>
+      <c r="P19" s="180" t="str">
         <f t="shared" si="6"/>
-        <v>$14717765,17</v>
+        <v>$137303,17</v>
       </c>
       <c r="Q19" s="43" t="str">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B20" s="62">
         <v>16</v>
       </c>
       <c r="C20" s="62" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F20" s="68">
         <v>5</v>
       </c>
       <c r="G20" s="134">
-        <v>208489.16</v>
+        <v>208615.16</v>
       </c>
       <c r="H20" s="129">
-        <f>134000+81000</f>
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="I20" s="70"/>
       <c r="J20" s="117">
         <f t="shared" si="0"/>
-        <v>-6510.8399999999965</v>
+        <v>-1384.8399999999965</v>
       </c>
       <c r="K20" s="71">
         <f t="shared" si="1"/>
@@ -3978,44 +3904,44 @@
       </c>
       <c r="L20" s="72">
         <f t="shared" si="2"/>
-        <v>9050</v>
+        <v>0</v>
       </c>
       <c r="M20" s="72">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>109265.395</v>
       </c>
       <c r="N20" s="114">
         <f t="shared" si="4"/>
-        <v>202539.16</v>
+        <v>107880.55500000001</v>
       </c>
       <c r="O20" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$202539,16</v>
+        <v>$107881,16</v>
       </c>
       <c r="P20" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$208615,16</v>
+        <v>$111117,16</v>
       </c>
       <c r="Q20" s="43" t="str">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B21" s="62">
         <v>15</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E21" s="62"/>
       <c r="F21" s="68">
@@ -4039,23 +3965,23 @@
       </c>
       <c r="L21" s="72">
         <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
+        <v>0</v>
       </c>
       <c r="M21" s="72">
         <f t="shared" si="3"/>
-        <v>327999.99999999994</v>
+        <v>179195.24779999998</v>
       </c>
       <c r="N21" s="114">
         <f t="shared" si="4"/>
-        <v>342841.99999999994</v>
+        <v>179195.24779999998</v>
       </c>
       <c r="O21" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$342842,15</v>
+        <v>$179195,15</v>
       </c>
       <c r="P21" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$353127,15</v>
+        <v>$184571,15</v>
       </c>
       <c r="Q21" s="43" t="str">
         <f t="shared" si="7"/>
@@ -4063,18 +3989,18 @@
       </c>
       <c r="S21" s="42"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B22" s="62">
         <v>20</v>
       </c>
       <c r="C22" s="62" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D22" s="62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="68">
@@ -4083,62 +4009,59 @@
       <c r="G22" s="134">
         <v>255041.2</v>
       </c>
-      <c r="H22" s="69">
-        <f>G22</f>
-        <v>255041.2</v>
-      </c>
+      <c r="H22" s="69"/>
       <c r="I22" s="70"/>
       <c r="J22" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>255041.2</v>
       </c>
       <c r="K22" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12752.060000000001</v>
       </c>
       <c r="L22" s="72">
         <f t="shared" si="2"/>
-        <v>11041</v>
+        <v>0</v>
       </c>
       <c r="M22" s="72">
         <f t="shared" si="3"/>
-        <v>244000</v>
+        <v>133303.7819</v>
       </c>
       <c r="N22" s="114">
         <f t="shared" si="4"/>
-        <v>255041</v>
+        <v>401097.04190000001</v>
       </c>
       <c r="O22" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$255041,20</v>
+        <v>$401097,20</v>
       </c>
       <c r="P22" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$262692,20</v>
+        <v>$413130,20</v>
       </c>
       <c r="Q22" s="43" t="str">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B23" s="62">
         <v>19</v>
       </c>
       <c r="C23" s="62" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F23" s="68">
         <v>5</v>
@@ -4161,44 +4084,44 @@
       </c>
       <c r="L23" s="72">
         <f t="shared" si="2"/>
-        <v>9050</v>
+        <v>0</v>
       </c>
       <c r="M23" s="72">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>109265.395</v>
       </c>
       <c r="N23" s="114">
         <f t="shared" si="4"/>
-        <v>209050</v>
+        <v>109265.395</v>
       </c>
       <c r="O23" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$209050,19</v>
+        <v>$109265,19</v>
       </c>
       <c r="P23" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$215322,19</v>
+        <v>$112543,19</v>
       </c>
       <c r="Q23" s="43" t="str">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="S23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B24" s="62">
         <v>18</v>
       </c>
       <c r="C24" s="62" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D24" s="151" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="68">
@@ -4222,33 +4145,33 @@
       </c>
       <c r="L24" s="72">
         <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
+        <v>0</v>
       </c>
       <c r="M24" s="72">
         <f t="shared" si="3"/>
-        <v>327999.99999999994</v>
+        <v>179195.24779999998</v>
       </c>
       <c r="N24" s="114">
         <f t="shared" si="4"/>
-        <v>342841.99999999994</v>
+        <v>179195.24779999998</v>
       </c>
       <c r="O24" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$342842,18</v>
+        <v>$179195,18</v>
       </c>
       <c r="P24" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$353127,18</v>
+        <v>$184571,18</v>
       </c>
       <c r="Q24" s="43" t="str">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -4259,11 +4182,11 @@
       </c>
       <c r="G25" s="54">
         <f t="shared" si="9"/>
-        <v>35239844.899999999</v>
+        <v>6213824.2700000014</v>
       </c>
       <c r="H25" s="60">
         <f t="shared" si="9"/>
-        <v>4658847.2699999996</v>
+        <v>5379748.5700000003</v>
       </c>
       <c r="I25" s="54">
         <f t="shared" si="9"/>
@@ -4271,19 +4194,19 @@
       </c>
       <c r="J25" s="60">
         <f t="shared" si="9"/>
-        <v>30580997.629999999</v>
+        <v>834075.7</v>
       </c>
       <c r="K25" s="60">
         <f t="shared" si="9"/>
-        <v>1529863.9645000002</v>
+        <v>42176.567000000003</v>
       </c>
       <c r="L25" s="60">
         <f t="shared" si="9"/>
-        <v>181000</v>
+        <v>0</v>
       </c>
       <c r="M25" s="60">
         <f t="shared" si="9"/>
-        <v>4000000</v>
+        <v>2185307.9</v>
       </c>
       <c r="N25" s="115"/>
       <c r="O25" s="77">
@@ -4295,97 +4218,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
       <c r="R26" s="104"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="181" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="174"/>
-      <c r="F28" s="174"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
-      <c r="O28" s="174"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="174"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="174"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="174"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="174"/>
-      <c r="N29" s="174"/>
-      <c r="O29" s="174"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="174"/>
-      <c r="L30" s="174"/>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
-      <c r="O30" s="174"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="174"/>
-      <c r="M31" s="174"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="174"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="174"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="174"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="174"/>
-      <c r="K32" s="174"/>
-      <c r="L32" s="174"/>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
-      <c r="O32" s="174"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="174"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="174"/>
-      <c r="G33" s="174"/>
-      <c r="H33" s="174"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="174"/>
-      <c r="K33" s="174"/>
-      <c r="L33" s="174"/>
-      <c r="M33" s="174"/>
-      <c r="N33" s="174"/>
-      <c r="O33" s="174"/>
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="189" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="185"/>
+      <c r="N28" s="185"/>
+      <c r="O28" s="185"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="185"/>
+      <c r="N29" s="185"/>
+      <c r="O29" s="185"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="185"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="185"/>
+      <c r="N30" s="185"/>
+      <c r="O30" s="185"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="185"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="185"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="185"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="185"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="185"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="185"/>
+      <c r="G33" s="185"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="185"/>
+      <c r="K33" s="185"/>
+      <c r="L33" s="185"/>
+      <c r="M33" s="185"/>
+      <c r="N33" s="185"/>
+      <c r="O33" s="185"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
